--- a/UNO-B-Board-BOM.xlsx
+++ b/UNO-B-Board-BOM.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="80">
   <si>
     <t>UNO B-Board BOM</t>
   </si>
@@ -211,7 +211,7 @@
     <t>BC857</t>
   </si>
   <si>
-    <t>R6,R17,R19,R25,R44,R50</t>
+    <t>R17,R19,R25,R44,R50</t>
   </si>
   <si>
     <t>C136889</t>
@@ -223,7 +223,7 @@
     <t>Resistor_SMD:R_1206_3216Metric</t>
   </si>
   <si>
-    <t>R9,R12</t>
+    <t>R6,R9,R12</t>
   </si>
   <si>
     <t>C844920</t>
@@ -259,7 +259,7 @@
     <t>56k</t>
   </si>
   <si>
-    <t>R29,R30,R35,R48,RV2</t>
+    <t>R29,R30,R35,R48</t>
   </si>
   <si>
     <t>C870758</t>
@@ -268,7 +268,16 @@
     <t>47k</t>
   </si>
   <si>
-    <t>R43,RV3</t>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>C844656</t>
+  </si>
+  <si>
+    <t>22k</t>
+  </si>
+  <si>
+    <t>RV2, RV3</t>
   </si>
   <si>
     <t>Potentiometer_THT:Potentiometer_Bourns_3296W_Vertical</t>
@@ -1315,7 +1324,7 @@
         <v>41</v>
       </c>
       <c r="C16" s="8">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="16" t="s">
@@ -1355,7 +1364,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="8">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="10" t="s">
@@ -1515,7 +1524,7 @@
         <v>57</v>
       </c>
       <c r="C21" s="8">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="16" t="s">
@@ -1555,20 +1564,20 @@
         <v>60</v>
       </c>
       <c r="C22" s="8">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="E22" s="16" t="s">
         <v>61</v>
       </c>
+      <c r="F22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="16" t="s">
-        <v>27</v>
-      </c>
+      <c r="I22" s="16"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1587,45 +1596,25 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23">
       <c r="A23" s="7">
         <v>17.0</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="8">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="16"/>
       <c r="F23" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="H23" s="1"/>
       <c r="I23" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="7">
@@ -1637,12 +1626,15 @@
       <c r="C24" s="8">
         <v>1.0</v>
       </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="8" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="16" t="s">
         <v>27</v>
       </c>
@@ -1669,19 +1661,19 @@
         <v>19.0</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="8">
         <v>1.0</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>27</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1706,62 +1698,75 @@
         <v>20.0</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="8">
+      <c r="F26" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="7">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="8">
         <v>2.0</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>72</v>
+      <c r="E27" s="8" t="s">
+        <v>75</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>73</v>
+      <c r="F27" s="8" t="s">
+        <v>76</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>74</v>
+      <c r="G27" s="8" t="s">
+        <v>77</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="H27" s="1"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
     </row>
     <row r="28">
       <c r="D28" s="1"/>
@@ -1997,7 +2002,7 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2047,7 +2052,7 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
